--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2164" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5897C9CE-5303-4FA0-84F3-39E9960E9DCC}"/>
+  <xr:revisionPtr revIDLastSave="2178" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C794CEE-111C-4391-9E3A-D5445D93465C}"/>
   <bookViews>
-    <workbookView xWindow="14076" yWindow="468" windowWidth="8964" windowHeight="10764" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10128" yWindow="1344" windowWidth="12912" windowHeight="10836" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="118">
   <si>
     <t>Market</t>
   </si>
@@ -385,6 +385,12 @@
   </si>
   <si>
     <t>102.47, -0.0, -2.47</t>
+  </si>
+  <si>
+    <t>15.51, 19.24, 65.25</t>
+  </si>
+  <si>
+    <t>122.34, -19.4, -2.95</t>
   </si>
 </sst>
 </file>
@@ -809,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F370"/>
+  <dimension ref="A1:F371"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -7059,6 +7065,13 @@
         <v>1</v>
       </c>
       <c r="C365" s="10"/>
+      <c r="D365" s="10">
+        <v>46265</v>
+      </c>
+      <c r="E365" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F365" s="10"/>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="6">
@@ -7071,6 +7084,16 @@
         <f>B366/B370</f>
         <v>0.65588305968235816</v>
       </c>
+      <c r="D366" s="6">
+        <v>2</v>
+      </c>
+      <c r="E366" s="8">
+        <v>4794475</v>
+      </c>
+      <c r="F366" s="7">
+        <f>E366/E370</f>
+        <v>0.62397632925090563</v>
+      </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="6">
@@ -7083,6 +7106,16 @@
         <f>B367/B370</f>
         <v>0.23349938987310165</v>
       </c>
+      <c r="D367" s="6">
+        <v>3</v>
+      </c>
+      <c r="E367" s="8">
+        <v>1521090</v>
+      </c>
+      <c r="F367" s="7">
+        <f>E367/E370</f>
+        <v>0.19796206146872392</v>
+      </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="6">
@@ -7095,8 +7128,18 @@
         <f>B368/B370</f>
         <v>6.4153937231433422E-2</v>
       </c>
-    </row>
-    <row r="369" spans="1:3">
+      <c r="D368" s="6">
+        <v>4</v>
+      </c>
+      <c r="E368" s="8">
+        <v>864400</v>
+      </c>
+      <c r="F368" s="7">
+        <f>E368/E370</f>
+        <v>0.11249722628744187</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369" s="6">
         <v>4</v>
       </c>
@@ -7107,8 +7150,18 @@
         <f>B369/B370</f>
         <v>4.646361321310679E-2</v>
       </c>
-    </row>
-    <row r="370" spans="1:3">
+      <c r="D369" s="6">
+        <v>1</v>
+      </c>
+      <c r="E369" s="8">
+        <v>503780</v>
+      </c>
+      <c r="F369" s="7">
+        <f>E369/E370</f>
+        <v>6.5564382992928577E-2</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
       <c r="B370" s="9">
         <f>SUM(B366:B369)</f>
         <v>7449270</v>
@@ -7117,6 +7170,17 @@
         <f>SUM(C366:C369)</f>
         <v>1.0000000000000002</v>
       </c>
+      <c r="E370" s="9">
+        <f>SUM(E366:E369)</f>
+        <v>7683745</v>
+      </c>
+      <c r="F370" s="7">
+        <f>SUM(F366:F369)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="F371" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9664,6 +9728,15 @@
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="D181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="182" spans="1:6" ht="57.6">
       <c r="A182" s="2">
@@ -9674,6 +9747,15 @@
       </c>
       <c r="C182" s="3" t="s">
         <v>114</v>
+      </c>
+      <c r="D182" s="2">
+        <v>46265</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -9683,6 +9765,13 @@
       </c>
       <c r="C183" s="13">
         <v>10410540</v>
+      </c>
+      <c r="D183" s="5"/>
+      <c r="E183" s="4">
+        <v>-265809</v>
+      </c>
+      <c r="F183" s="13">
+        <v>10614480</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/05-Profit-&-Balance-by-Market.xlsx
+++ b/Excel/05-Profit-&-Balance-by-Market.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2178" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C794CEE-111C-4391-9E3A-D5445D93465C}"/>
+  <xr:revisionPtr revIDLastSave="2195" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD535EFE-B1B6-4FA5-B61C-C1C66476C743}"/>
   <bookViews>
-    <workbookView xWindow="10128" yWindow="1344" windowWidth="12912" windowHeight="10836" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5148" yWindow="1416" windowWidth="16632" windowHeight="11496" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Amt by Period" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="121">
   <si>
     <t>Market</t>
   </si>
@@ -391,6 +391,15 @@
   </si>
   <si>
     <t>122.34, -19.4, -2.95</t>
+  </si>
+  <si>
+    <t>15.39, 19.55, 65.06</t>
+  </si>
+  <si>
+    <t>156.2, -52.44, -3.76</t>
+  </si>
+  <si>
+    <t>PROSPECT</t>
   </si>
 </sst>
 </file>
@@ -481,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -501,6 +510,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -815,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F4CBCB-3344-43F6-9D2A-BD9A74C7367A}">
-  <dimension ref="A1:F371"/>
+  <dimension ref="A1:F377"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.109375" style="6" bestFit="1" customWidth="1"/>
@@ -7182,6 +7192,73 @@
     <row r="371" spans="1:6">
       <c r="F371" s="7"/>
     </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="10">
+        <v>46297</v>
+      </c>
+      <c r="B372" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C372" s="10"/>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="6">
+        <v>2</v>
+      </c>
+      <c r="B373" s="8">
+        <v>4540025</v>
+      </c>
+      <c r="C373" s="7">
+        <f>B373/B377</f>
+        <v>0.585311973431624</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="6">
+        <v>4</v>
+      </c>
+      <c r="B374" s="8">
+        <v>1713200</v>
+      </c>
+      <c r="C374" s="7">
+        <f>B374/B377</f>
+        <v>0.22087025355214082</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="6">
+        <v>3</v>
+      </c>
+      <c r="B375" s="8">
+        <v>841205</v>
+      </c>
+      <c r="C375" s="7">
+        <f>B375/B377</f>
+        <v>0.10845036285274844</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="6">
+        <v>1</v>
+      </c>
+      <c r="B376" s="8">
+        <v>662160</v>
+      </c>
+      <c r="C376" s="7">
+        <f>B376/B377</f>
+        <v>8.5367410163486784E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="B377" s="9">
+        <f>SUM(B373:B376)</f>
+        <v>7756590</v>
+      </c>
+      <c r="C377" s="7">
+        <f>SUM(C373:C376)</f>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7189,7 +7266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -9774,6 +9851,53 @@
         <v>10614480</v>
       </c>
     </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="57.6">
+      <c r="A186" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="5"/>
+      <c r="B187" s="4">
+        <v>-209337</v>
+      </c>
+      <c r="C187" s="13">
+        <v>10406480</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="C188">
+        <v>10766480</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="C189" s="15">
+        <f>C188-C187</f>
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="C190" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
